--- a/artfynd/A 5774-2024 artfynd.xlsx
+++ b/artfynd/A 5774-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467913</v>
+        <v>121467756</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>98011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531472</v>
+        <v>531748</v>
       </c>
       <c r="R2" t="n">
-        <v>6516456</v>
+        <v>6516209</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467756</v>
+        <v>121467758</v>
       </c>
       <c r="B3" t="n">
         <v>98011</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531748</v>
+        <v>531717</v>
       </c>
       <c r="R3" t="n">
-        <v>6516209</v>
+        <v>6516231</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467758</v>
+        <v>121467913</v>
       </c>
       <c r="B4" t="n">
-        <v>98011</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531717</v>
+        <v>531472</v>
       </c>
       <c r="R4" t="n">
-        <v>6516231</v>
+        <v>6516456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5774-2024 artfynd.xlsx
+++ b/artfynd/A 5774-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467756</v>
+        <v>121467758</v>
       </c>
       <c r="B2" t="n">
-        <v>98011</v>
+        <v>98012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531748</v>
+        <v>531717</v>
       </c>
       <c r="R2" t="n">
-        <v>6516209</v>
+        <v>6516231</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467758</v>
+        <v>121467913</v>
       </c>
       <c r="B3" t="n">
-        <v>98011</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531717</v>
+        <v>531472</v>
       </c>
       <c r="R3" t="n">
-        <v>6516231</v>
+        <v>6516456</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467913</v>
+        <v>121467756</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>98012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531472</v>
+        <v>531748</v>
       </c>
       <c r="R4" t="n">
-        <v>6516456</v>
+        <v>6516209</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5774-2024 artfynd.xlsx
+++ b/artfynd/A 5774-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467758</v>
+        <v>121467913</v>
       </c>
       <c r="B2" t="n">
-        <v>98012</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531717</v>
+        <v>531472</v>
       </c>
       <c r="R2" t="n">
-        <v>6516231</v>
+        <v>6516456</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467913</v>
+        <v>121467758</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>98015</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531472</v>
+        <v>531717</v>
       </c>
       <c r="R3" t="n">
-        <v>6516456</v>
+        <v>6516231</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
         <v>121467756</v>
       </c>
       <c r="B4" t="n">
-        <v>98012</v>
+        <v>98015</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 5774-2024 artfynd.xlsx
+++ b/artfynd/A 5774-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467913</v>
+        <v>121467758</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>98015</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531472</v>
+        <v>531717</v>
       </c>
       <c r="R2" t="n">
-        <v>6516456</v>
+        <v>6516231</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467758</v>
+        <v>121467756</v>
       </c>
       <c r="B3" t="n">
         <v>98015</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531717</v>
+        <v>531748</v>
       </c>
       <c r="R3" t="n">
-        <v>6516231</v>
+        <v>6516209</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467756</v>
+        <v>121467913</v>
       </c>
       <c r="B4" t="n">
-        <v>98015</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531748</v>
+        <v>531472</v>
       </c>
       <c r="R4" t="n">
-        <v>6516209</v>
+        <v>6516456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5774-2024 artfynd.xlsx
+++ b/artfynd/A 5774-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467758</v>
+        <v>121467913</v>
       </c>
       <c r="B2" t="n">
-        <v>98015</v>
+        <v>57371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531717</v>
+        <v>531472</v>
       </c>
       <c r="R2" t="n">
-        <v>6516231</v>
+        <v>6516456</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467756</v>
+        <v>121467758</v>
       </c>
       <c r="B3" t="n">
-        <v>98015</v>
+        <v>98021</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531748</v>
+        <v>531717</v>
       </c>
       <c r="R3" t="n">
-        <v>6516209</v>
+        <v>6516231</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467913</v>
+        <v>121467756</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>98021</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531472</v>
+        <v>531748</v>
       </c>
       <c r="R4" t="n">
-        <v>6516456</v>
+        <v>6516209</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5774-2024 artfynd.xlsx
+++ b/artfynd/A 5774-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467913</v>
+        <v>121467756</v>
       </c>
       <c r="B2" t="n">
-        <v>57371</v>
+        <v>98022</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531472</v>
+        <v>531748</v>
       </c>
       <c r="R2" t="n">
-        <v>6516456</v>
+        <v>6516209</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +784,7 @@
         <v>121467758</v>
       </c>
       <c r="B3" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467756</v>
+        <v>121467913</v>
       </c>
       <c r="B4" t="n">
-        <v>98021</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531748</v>
+        <v>531472</v>
       </c>
       <c r="R4" t="n">
-        <v>6516209</v>
+        <v>6516456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5774-2024 artfynd.xlsx
+++ b/artfynd/A 5774-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467758</v>
+        <v>121467913</v>
       </c>
       <c r="B3" t="n">
-        <v>98022</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531717</v>
+        <v>531472</v>
       </c>
       <c r="R3" t="n">
-        <v>6516231</v>
+        <v>6516456</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467913</v>
+        <v>121467758</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>98022</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531472</v>
+        <v>531717</v>
       </c>
       <c r="R4" t="n">
-        <v>6516456</v>
+        <v>6516231</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5774-2024 artfynd.xlsx
+++ b/artfynd/A 5774-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467913</v>
+        <v>121467758</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>98022</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531472</v>
+        <v>531717</v>
       </c>
       <c r="R3" t="n">
-        <v>6516456</v>
+        <v>6516231</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467758</v>
+        <v>121467913</v>
       </c>
       <c r="B4" t="n">
-        <v>98022</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531717</v>
+        <v>531472</v>
       </c>
       <c r="R4" t="n">
-        <v>6516231</v>
+        <v>6516456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5774-2024 artfynd.xlsx
+++ b/artfynd/A 5774-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467756</v>
+        <v>121467758</v>
       </c>
       <c r="B2" t="n">
         <v>98022</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531748</v>
+        <v>531717</v>
       </c>
       <c r="R2" t="n">
-        <v>6516209</v>
+        <v>6516231</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467758</v>
+        <v>121467756</v>
       </c>
       <c r="B3" t="n">
         <v>98022</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531717</v>
+        <v>531748</v>
       </c>
       <c r="R3" t="n">
-        <v>6516231</v>
+        <v>6516209</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 5774-2024 artfynd.xlsx
+++ b/artfynd/A 5774-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467758</v>
+        <v>121467913</v>
       </c>
       <c r="B2" t="n">
-        <v>98022</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531717</v>
+        <v>531472</v>
       </c>
       <c r="R2" t="n">
-        <v>6516231</v>
+        <v>6516456</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +784,7 @@
         <v>121467756</v>
       </c>
       <c r="B3" t="n">
-        <v>98022</v>
+        <v>98030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467913</v>
+        <v>121467758</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>98030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531472</v>
+        <v>531717</v>
       </c>
       <c r="R4" t="n">
-        <v>6516456</v>
+        <v>6516231</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5774-2024 artfynd.xlsx
+++ b/artfynd/A 5774-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467913</v>
+        <v>121467758</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>98030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531472</v>
+        <v>531717</v>
       </c>
       <c r="R2" t="n">
-        <v>6516456</v>
+        <v>6516231</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121467758</v>
+        <v>121467756</v>
       </c>
       <c r="B3" t="n">
         <v>98030</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531717</v>
+        <v>531748</v>
       </c>
       <c r="R3" t="n">
-        <v>6516231</v>
+        <v>6516209</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467756</v>
+        <v>121467913</v>
       </c>
       <c r="B4" t="n">
-        <v>98030</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531748</v>
+        <v>531472</v>
       </c>
       <c r="R4" t="n">
-        <v>6516209</v>
+        <v>6516456</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5774-2024 artfynd.xlsx
+++ b/artfynd/A 5774-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121467758</v>
+        <v>121467913</v>
       </c>
       <c r="B2" t="n">
-        <v>98030</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531717</v>
+        <v>531472</v>
       </c>
       <c r="R2" t="n">
-        <v>6516231</v>
+        <v>6516456</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121467913</v>
+        <v>121467758</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>98030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531472</v>
+        <v>531717</v>
       </c>
       <c r="R4" t="n">
-        <v>6516456</v>
+        <v>6516231</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
